--- a/party-comparison-updated-v47.xlsx
+++ b/party-comparison-updated-v47.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einat\git_5050\party-comparison\party-comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_D1DDDA8EB4B254C07C41EF8C73322E2CA5AA7392" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6DA2A8-2512-4045-BE63-06DF617DB2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7580" uniqueCount="1815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7580" uniqueCount="1817">
   <si>
     <t>מפלגה</t>
   </si>
@@ -5565,6 +5565,12 @@
   </si>
   <si>
     <t>506</t>
+  </si>
+  <si>
+    <t>מיקום לא ידוע</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מיקום לא ידוע </t>
   </si>
 </sst>
 </file>
@@ -43745,10 +43751,10 @@
         <v>255</v>
       </c>
       <c r="D191" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E191" t="s">
-        <v>102</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -43765,7 +43771,7 @@
         <v>7</v>
       </c>
       <c r="E192" t="s">
-        <v>102</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -44375,15 +44381,15 @@
       </c>
       <c r="C8" s="10">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,A8,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B8)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="10">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,A8,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B8)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="13">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>1767</v>
@@ -44647,15 +44653,15 @@
       </c>
       <c r="C16" s="12">
         <f>SUM(C2:C15)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="12">
         <f>SUM(D2:D15)</f>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" s="16">
         <f t="shared" si="0"/>
-        <v>0.26050420168067229</v>
+        <v>0.25210084033613445</v>
       </c>
       <c r="G16">
         <f>SUM(G2:G15)</f>
@@ -45052,15 +45058,15 @@
       </c>
       <c r="E11">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="H11">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C11)</f>
@@ -46132,15 +46138,15 @@
       </c>
       <c r="E41">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H41">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C41)</f>
@@ -46672,15 +46678,15 @@
       </c>
       <c r="E56">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H56">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C56)</f>
@@ -47212,15 +47218,15 @@
       </c>
       <c r="E71">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71">
         <f t="shared" si="4"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H71">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C71)</f>
@@ -47752,15 +47758,15 @@
       </c>
       <c r="E86">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C86,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D86)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F86">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C86,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D86)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G86">
         <f t="shared" si="4"/>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="H86">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C86)</f>
@@ -48292,15 +48298,15 @@
       </c>
       <c r="E101">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C101,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D101)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C101,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D101)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101">
         <f t="shared" si="6"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H101">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C101)</f>
@@ -48832,15 +48838,15 @@
       </c>
       <c r="E116">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C116,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D116)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F116">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C116,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D116)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G116">
         <f t="shared" si="6"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H116">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C116)</f>
@@ -49372,15 +49378,15 @@
       </c>
       <c r="E131">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C131,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D131)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F131">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C131,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D131)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G131">
         <f t="shared" si="8"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H131">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C131)</f>
@@ -49912,15 +49918,15 @@
       </c>
       <c r="E146">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C146,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D146)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F146">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C146,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D146)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G146">
         <f t="shared" si="8"/>
-        <v>0.33333333333333331</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="H146">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C146)</f>
